--- a/재원/241220_데이터 정리_재원.xlsx
+++ b/재원/241220_데이터 정리_재원.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\Team3\재원\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA1F8C6-6178-4EAD-BACD-C4828FFCA2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9623F869-55E3-4E82-A087-F4D1BD2FA753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F881B30-87A6-47BA-921E-F312CF413D6B}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8F881B30-87A6-47BA-921E-F312CF413D6B}"/>
   </bookViews>
   <sheets>
-    <sheet name="데이터목록" sheetId="1" r:id="rId1"/>
-    <sheet name="데이터QnA" sheetId="2" r:id="rId2"/>
+    <sheet name="샘플 데이터목록" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="데이터QnA" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="342">
   <si>
     <t>테이블명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1418,6 +1419,10 @@
   </si>
   <si>
     <t>VOD subsr과 일치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가사항</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1531,12 +1536,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CD3AF13D-B442-47FA-8093-002D4D3FB388}" name="표2" displayName="표2" ref="A1:D1048575" totalsRowShown="0">
-  <autoFilter ref="A1:D1048575" xr:uid="{CD3AF13D-B442-47FA-8093-002D4D3FB388}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CD3AF13D-B442-47FA-8093-002D4D3FB388}" name="표2" displayName="표2" ref="A1:E1048575" totalsRowShown="0">
+  <autoFilter ref="A1:E1048575" xr:uid="{CD3AF13D-B442-47FA-8093-002D4D3FB388}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8C4B311C-76F6-4C86-9451-4515A4E9FEC9}" name="테이블명"/>
     <tableColumn id="2" xr3:uid="{A2B917BE-4E8C-4F67-8436-7B3883ECAB43}" name="피쳐"/>
     <tableColumn id="3" xr3:uid="{A066D825-C74F-48B6-BEFC-B5AAC07E64F9}" name="피쳐설명"/>
+    <tableColumn id="11" xr3:uid="{BC4D0D3F-37B9-4C16-95E8-0B6BF10A4094}" name="추가사항"/>
     <tableColumn id="4" xr3:uid="{190BA9A6-C6F5-4191-BCA2-9B062803414C}" name="구분"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1860,16 +1866,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A906B8AF-C48A-492E-9145-ACA37A0E9800}">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1880,10 +1886,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1905,7 +1914,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1916,7 +1925,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1927,7 +1936,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -1938,7 +1947,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1949,7 +1958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -1960,7 +1969,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1971,7 +1980,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1982,7 +1991,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1993,7 +2002,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -2004,7 +2013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -2015,7 +2024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -2026,7 +2035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -2037,7 +2046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -3587,6 +3596,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72D2345-7166-44C1-9911-741F7A8F68D1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD70DBF5-0B99-4949-8084-B9C276DD2FBD}">
   <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
